--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.0-Official-Lean.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.0-Official-Lean.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbf9b17eb7f704d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R360653011a78458f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R7764b58312754340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R6ad346414db54781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="Rdb636092630f4919"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R5fd6d2bdd543499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="R4d7533b2c69f458b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R9176cfff330c4b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R110f8c19d34d4160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" r:id="Rbe46468f961a4a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R8267e18c0b9141e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善中" sheetId="3" r:id="R387a6ad687a34abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブログ診断" sheetId="4" r:id="R21bc30e4ae3348e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="処理ログ" sheetId="5" r:id="R8395e2463e984cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="6" r:id="R1f877b33a6124c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SearchConsole_Data" sheetId="7" r:id="Rc6fb9065b1304280"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Queue" sheetId="8" r:id="R8fbce6320e4e4dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improvement_Log" sheetId="9" r:id="R94fd23da9dd142f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -502,11 +502,10 @@
         <x:v>今日の改善残数</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:f>COUNTA('今日の改善'!A2:A6)</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>5件を上限表示</x:v>
+        <x:v>初期2件・最大6件</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -514,11 +513,10 @@
         <x:v>測定対象</x:v>
       </x:c>
       <x:c r="B11" t="n">
-        <x:f>COUNTA('改善中'!A2:A200)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>週1回・最大2か月</x:v>
+        <x:v>7日・14日・21日・28日</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4197,8 +4195,7 @@
         <x:v>今日の改善数</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:f>COUNTA('今日の改善'!A2:A6)</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>改善候補</x:v>
@@ -5330,10 +5327,10 @@
         <x:v>Candidate Limit</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>改善候補は30件で停止</x:v>
+        <x:v>改善候補は10件で停止</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>不可</x:v>
@@ -5344,10 +5341,10 @@
         <x:v>Today Limit</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>今日の改善は上位5件</x:v>
+        <x:v>今日の改善は初期2件、最大6件</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>不可</x:v>
@@ -5358,10 +5355,10 @@
         <x:v>Measurement Weeks</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>週1回・最大2か月</x:v>
+        <x:v>7日・14日・21日・28日の4回測定</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>不可</x:v>
